--- a/Input_opti.xlsx
+++ b/Input_opti.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{880F9C71-01DA-49A0-9100-179F068CC098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15746423-C3A4-46DB-B811-9188BBC98E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11860" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
     <sheet name="Employee" sheetId="2" r:id="rId2"/>
+    <sheet name="DaysOff" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Event</t>
   </si>
@@ -181,6 +182,24 @@
   </si>
   <si>
     <t>30.4.2025</t>
+  </si>
+  <si>
+    <t>01.05.2025</t>
+  </si>
+  <si>
+    <t>02.05.2025</t>
+  </si>
+  <si>
+    <t>03.05.2025</t>
+  </si>
+  <si>
+    <t>04.05.2025</t>
+  </si>
+  <si>
+    <t>05.05.2025</t>
+  </si>
+  <si>
+    <t>06.05.2025</t>
   </si>
 </sst>
 </file>
@@ -1109,4 +1128,136 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6FB8F10-AD87-46D0-B8B5-EE2B4F86A1AB}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>